--- a/data/normalized/basidia_filled.xlsx
+++ b/data/normalized/basidia_filled.xlsx
@@ -519,1138 +519,718 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>A. mortenii</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>31.14166666666667</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>39.5</v>
+        <v>73</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>8.579166666666666</v>
+        <v>17.4</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.891666666666666</v>
+        <v>7.375</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="F3" t="n">
-        <v>44.78</v>
+        <v>48.5</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I3" t="n">
-        <v>12.688</v>
+        <v>11.5625</v>
       </c>
       <c r="J3" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>5.486363636363635</v>
+        <v>5.4375</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amanita oberwinkleriana</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Roanokensis</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>38.5</v>
       </c>
       <c r="F4" t="n">
-        <v>35.16</v>
+        <v>42.35714285714285</v>
       </c>
       <c r="G4" t="n">
-        <v>39.5</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>11.628</v>
+        <v>9.714285714285714</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>5.404347826086957</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11.32352941176471</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>7.117647058823529</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amanita sp. aurorae</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>38.64285714285715</v>
-      </c>
-      <c r="G6" t="n">
-        <v>42</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12.85714285714286</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4.914285714285714</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>30217</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amanita sp 44</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E7" t="n">
-        <v>56</v>
-      </c>
-      <c r="F7" t="n">
-        <v>68.53333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>81</v>
-      </c>
-      <c r="H7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>16.11666666666667</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" t="n">
-        <v>15</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>9.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>35</v>
-      </c>
-      <c r="F8" t="n">
-        <v>41.39285714285715</v>
-      </c>
-      <c r="G8" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11.86666666666667</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30219</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amanita sp longicuneus</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>15</v>
-      </c>
-      <c r="E9" t="n">
-        <v>37</v>
-      </c>
-      <c r="F9" t="n">
-        <v>49.26666666666667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>57</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amanita rhacopus</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E10" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>46.56818181818182</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>15.40909090909091</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>15</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5.863636363636363</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>30208_2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amanita frostiana</t>
+          <t>Amanita aff. citrina</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>46</v>
-      </c>
-      <c r="F11" t="n">
-        <v>53.93333333333333</v>
-      </c>
-      <c r="G11" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amanita frostiana</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="F12" t="n">
-        <v>49.46666666666667</v>
+        <v>44.5</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="I12" t="n">
-        <v>12.70666666666667</v>
+        <v>10.5625</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>5.092857142857143</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amanita muscaria var. guessowii</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" t="n">
-        <v>52</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.85714285714286</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>10</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>15</v>
-      </c>
-      <c r="E14" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>59</v>
-      </c>
-      <c r="H14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>14.53333333333333</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.142857142857143</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amanita2</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>51</v>
-      </c>
-      <c r="G15" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>15.18181818181818</v>
-      </c>
-      <c r="J15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amanita amerivirosa</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>59</v>
-      </c>
-      <c r="H16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>13.14285714285714</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5.285714285714286</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30230_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amanita muscaria var. guessowii</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>50</v>
-      </c>
-      <c r="H17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30230_3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amanita muscaria var. guessowii</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>39</v>
-      </c>
-      <c r="G18" t="n">
-        <v>39</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30230_4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A. mortenii</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F19" t="n">
-        <v>66.84999999999999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>73</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>7.375</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30230_5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>44</v>
-      </c>
-      <c r="H20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>14.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>30230_6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1671,12 +1251,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30230_7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amanita flavoconia</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1684,58 +1264,30 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>13</v>
-      </c>
-      <c r="E22" t="n">
-        <v>35</v>
-      </c>
-      <c r="F22" t="n">
-        <v>38.88461538461539</v>
-      </c>
-      <c r="G22" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11.41666666666667</v>
-      </c>
-      <c r="J22" t="n">
-        <v>13</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4.181818181818182</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>7</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>30230_8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amanita porphyria</t>
+          <t>Amanita aff. rubescens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1743,407 +1295,239 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>42.66666666666666</v>
-      </c>
-      <c r="G23" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>12.66666666666667</v>
-      </c>
-      <c r="J23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>14</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="F24" t="n">
-        <v>52.4</v>
+        <v>46.8</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I24" t="n">
-        <v>13.63333333333333</v>
+        <v>14.53333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>6.178571428571429</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" t="n">
-        <v>44</v>
-      </c>
-      <c r="F25" t="n">
-        <v>53.54166666666666</v>
-      </c>
-      <c r="G25" t="n">
-        <v>67</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" t="n">
-        <v>13.20833333333333</v>
-      </c>
-      <c r="J25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>11</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.818181818181818</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>8</v>
-      </c>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amanita flavoconia</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="n">
-        <v>33</v>
-      </c>
-      <c r="F26" t="n">
-        <v>38.15</v>
-      </c>
-      <c r="G26" t="n">
-        <v>43</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.5</v>
-      </c>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30193_2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amanita flavoconia</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>34</v>
-      </c>
-      <c r="F27" t="n">
-        <v>37.57142857142857</v>
-      </c>
-      <c r="G27" t="n">
-        <v>40</v>
-      </c>
-      <c r="H27" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" t="n">
-        <v>9.833333333333334</v>
-      </c>
-      <c r="J27" t="n">
-        <v>14</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5.166666666666667</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>8</v>
-      </c>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30193_3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amanita porphyria</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F28" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>6.777777777777778</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9</v>
-      </c>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30257_2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita albiceps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>52</v>
-      </c>
-      <c r="H29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>11.5625</v>
-      </c>
-      <c r="J29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>5.4375</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2157,93 +1541,121 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="F30" t="n">
-        <v>56.86363636363637</v>
+        <v>52.5</v>
       </c>
       <c r="G30" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I30" t="n">
-        <v>15</v>
+        <v>13.14285714285714</v>
       </c>
       <c r="J30" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="K30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>5.863636363636363</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amanita muscaria var. guessowii</t>
+          <t>Amanita amerivirosa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>49</v>
+      </c>
+      <c r="F31" t="n">
+        <v>56.86363636363637</v>
+      </c>
+      <c r="G31" t="n">
+        <v>69</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12</v>
+      </c>
+      <c r="I31" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" t="n">
+        <v>25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5.863636363636363</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amanita muscaria var. guessowii</t>
+          <t>Amanita amerivirosa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2264,225 +1676,169 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amanita sp.</t>
+          <t>Amanita amerivirosa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Amidella</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12</v>
-      </c>
-      <c r="E33" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>44.66666666666666</v>
-      </c>
-      <c r="G33" t="n">
-        <v>51</v>
-      </c>
-      <c r="H33" t="n">
-        <v>9</v>
-      </c>
-      <c r="I33" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="J33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>4.590909090909091</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>6.5</v>
-      </c>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita amerivirosa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>42.35714285714285</v>
-      </c>
-      <c r="G34" t="n">
-        <v>49</v>
-      </c>
-      <c r="H34" t="n">
-        <v>9</v>
-      </c>
-      <c r="I34" t="n">
-        <v>9.714285714285714</v>
-      </c>
-      <c r="J34" t="n">
-        <v>11</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3</v>
-      </c>
-      <c r="P34" t="n">
-        <v>4.857142857142857</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7</v>
-      </c>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>31.14166666666667</v>
+      </c>
+      <c r="G35" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8.579166666666666</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5.891666666666666</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amanita sp. 61</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>48</v>
-      </c>
-      <c r="F36" t="n">
-        <v>65.375</v>
-      </c>
-      <c r="G36" t="n">
-        <v>77</v>
-      </c>
-      <c r="H36" t="n">
-        <v>13</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16.625</v>
-      </c>
-      <c r="J36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>8</v>
-      </c>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2503,17 +1859,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2534,17 +1890,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>30275</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2565,17 +1921,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita bisporigera</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2596,17 +1952,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amanita sp. 61</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2627,135 +1983,107 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amanita velatipes</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>34.5</v>
+        <v>37</v>
       </c>
       <c r="F42" t="n">
-        <v>43.28571428571428</v>
+        <v>40.25</v>
       </c>
       <c r="G42" t="n">
-        <v>49</v>
+        <v>43.5</v>
       </c>
       <c r="H42" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="P42" t="n">
-        <v>5.642857142857143</v>
+        <v>5.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>10</v>
-      </c>
-      <c r="I43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>7.5</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2776,17 +2104,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2807,17 +2135,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2838,46 +2166,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Amanita sp NY06</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
-        <v>11</v>
-      </c>
-      <c r="I47" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" t="n">
-        <v>11</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -2885,17 +2197,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amanita sp NY06</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2916,12 +2228,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amanita flavoconia</t>
+          <t>Amanita brunnescens</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2947,17 +2259,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amanita frostiana</t>
+          <t>Amanita cf. lavendula</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2978,12 +2290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita cf. lavendula</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2991,63 +2303,35 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="F51" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>49</v>
-      </c>
-      <c r="H51" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>10.5625</v>
-      </c>
-      <c r="J51" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K51" t="n">
-        <v>8</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>5</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>6</v>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>30231</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita coryli</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -3068,17 +2352,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita coryli</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -3099,12 +2383,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30250_2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amanita rhacopus</t>
+          <t>Amanita coryli</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3130,43 +2414,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amanita rhacopus</t>
+          <t>Amanita flavoconia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13</v>
+      </c>
+      <c r="E55" t="n">
+        <v>35</v>
+      </c>
+      <c r="F55" t="n">
+        <v>38.88461538461539</v>
+      </c>
+      <c r="G55" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>11.41666666666667</v>
+      </c>
+      <c r="J55" t="n">
+        <v>13</v>
+      </c>
+      <c r="K55" t="n">
+        <v>11</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3</v>
+      </c>
+      <c r="P55" t="n">
+        <v>4.181818181818182</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amanita solaniolens</t>
+          <t>Amanita flavoconia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3174,30 +2486,58 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="n">
+        <v>33</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="G56" t="n">
+        <v>43</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amanita solaniolens</t>
+          <t>Amanita flavoconia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3205,35 +2545,63 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>9</v>
+      </c>
+      <c r="E57" t="n">
+        <v>34</v>
+      </c>
+      <c r="F57" t="n">
+        <v>37.57142857142857</v>
+      </c>
+      <c r="G57" t="n">
+        <v>40</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.833333333333334</v>
+      </c>
+      <c r="J57" t="n">
+        <v>14</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>30228</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita flavoconia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -3313,97 +2681,97 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>30239</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amanita virginiana</t>
+          <t>Amanita flavorubens</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Caesareae</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F60" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>4</v>
-      </c>
-      <c r="P60" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4</v>
-      </c>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>30190</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>Amanita frostiana</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>46</v>
+      </c>
+      <c r="F61" t="n">
+        <v>53.93333333333333</v>
+      </c>
+      <c r="G61" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>15</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3416,35 +2784,63 @@
           <t>Amanita</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>49.46666666666667</v>
+      </c>
+      <c r="G62" t="n">
+        <v>60</v>
+      </c>
+      <c r="H62" t="n">
+        <v>11</v>
+      </c>
+      <c r="I62" t="n">
+        <v>12.70666666666667</v>
+      </c>
+      <c r="J62" t="n">
+        <v>15</v>
+      </c>
+      <c r="K62" t="n">
+        <v>14</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P62" t="n">
+        <v>5.092857142857143</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Amanita fulva</t>
+          <t>Amanita frostiana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3465,17 +2861,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amanita coryli</t>
+          <t>Amanita frostiana</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -3496,17 +2892,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30245</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amanita fulva</t>
+          <t>Amanita frostiana</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -3527,17 +2923,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita fulva</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3558,12 +2954,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amanita sp. 'balmei'</t>
+          <t>Amanita fulva</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3589,17 +2985,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita fulva</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3620,12 +3016,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amanita sp NY06</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3634,28 +3030,28 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>32</v>
+        <v>38.5</v>
       </c>
       <c r="F69" t="n">
-        <v>32</v>
+        <v>48.1</v>
       </c>
       <c r="G69" t="n">
-        <v>32</v>
+        <v>53.5</v>
       </c>
       <c r="H69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>11.1</v>
       </c>
       <c r="J69" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3664,26 +3060,32 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3</v>
+      </c>
+      <c r="P69" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Amanita coryli</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -3704,17 +3106,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>30224</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3735,17 +3137,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>30252</t>
+          <t>30223_2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3766,17 +3168,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30223_3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3797,17 +3199,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>30254</t>
+          <t>30224_2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita multisquamosa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3828,110 +3230,194 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amanita fulva</t>
+          <t>Amanita muscaria var. guessowii</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" t="n">
+        <v>10</v>
+      </c>
+      <c r="I75" t="n">
+        <v>11.85714285714286</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Amanita rhacopus</t>
+          <t>Amanita muscaria var. guessowii</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="J76" t="n">
+        <v>12</v>
+      </c>
+      <c r="K76" t="n">
+        <v>9</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita muscaria var. guessowii</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F77" t="n">
+        <v>39</v>
+      </c>
+      <c r="G77" t="n">
+        <v>39</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J77" t="n">
+        <v>10</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita muscaria var. guessowii</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3952,17 +3438,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita muscaria var. guessowii</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3983,48 +3469,76 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>30260</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amanita solaniolens</t>
+          <t>Amanita oberwinkleriana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+          <t>Roanokensis</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>25</v>
+      </c>
+      <c r="E80" t="n">
+        <v>32</v>
+      </c>
+      <c r="F80" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="G80" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" t="n">
+        <v>11.628</v>
+      </c>
+      <c r="J80" t="n">
+        <v>13</v>
+      </c>
+      <c r="K80" t="n">
+        <v>23</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2</v>
+      </c>
+      <c r="P80" t="n">
+        <v>5.404347826086957</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>30261</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amanita frostiana</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -4045,12 +3559,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>30251</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amanita sp. subnigra</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4076,17 +3590,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -4107,17 +3621,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>30280_2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -4138,17 +3652,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>30280_3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -4169,17 +3683,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>30280_4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amanita amerivirosa</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -4200,12 +3714,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>30280_5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Amanita sp. jakeslandingensis</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4231,17 +3745,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30280_6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amanita amerivirosa</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -4262,17 +3776,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30280_7</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amanita amerivirosa</t>
+          <t>Amanita populiphila</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -4293,12 +3807,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amanita sp. rubescens</t>
+          <t>Amanita porphyria</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4306,30 +3820,58 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>15</v>
+      </c>
+      <c r="E90" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>42.66666666666666</v>
+      </c>
+      <c r="G90" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="J90" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>14</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P90" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amanita brunnescens</t>
+          <t>Amanita porphyria</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4337,35 +3879,63 @@
           <t>Validae</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="n">
+        <v>30</v>
+      </c>
+      <c r="F91" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="J91" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>10</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>5</v>
+      </c>
+      <c r="P91" t="n">
+        <v>6.777777777777778</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>Amanita porphyria</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -4386,17 +3956,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30274</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Amanita sp.</t>
+          <t>Amanita porphyria</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Amidella</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -4417,48 +3987,76 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>Amanita rhacopus</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>22</v>
+      </c>
+      <c r="E94" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>46.56818181818182</v>
+      </c>
+      <c r="G94" t="n">
+        <v>55</v>
+      </c>
+      <c r="H94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>15.40909090909091</v>
+      </c>
+      <c r="J94" t="n">
+        <v>17</v>
+      </c>
+      <c r="K94" t="n">
+        <v>15</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>5</v>
+      </c>
+      <c r="P94" t="n">
+        <v>5.863636363636363</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Amanita sp.</t>
+          <t>Amanita rhacopus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -4479,17 +4077,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amanita bisporigera</t>
+          <t>Amanita rhacopus</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -4510,12 +4108,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Amanita sp 61</t>
+          <t>Amanita rhacopus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4541,17 +4139,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>30279</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita solaniolens</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -4572,17 +4170,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita solaniolens</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -4603,17 +4201,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Amanita sp 44</t>
+          <t>Amanita solaniolens</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Validae</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -4634,7 +4232,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4647,35 +4245,63 @@
           <t>Vaginatae</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>15</v>
+      </c>
+      <c r="E101" t="n">
+        <v>56</v>
+      </c>
+      <c r="F101" t="n">
+        <v>68.53333333333333</v>
+      </c>
+      <c r="G101" t="n">
+        <v>81</v>
+      </c>
+      <c r="H101" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I101" t="n">
+        <v>16.11666666666667</v>
+      </c>
+      <c r="J101" t="n">
+        <v>19</v>
+      </c>
+      <c r="K101" t="n">
+        <v>15</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>6</v>
+      </c>
+      <c r="P101" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Amanita flavorubens</t>
+          <t>Amanita sp 44</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -4696,17 +4322,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita sp 44</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -4758,17 +4384,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Amanita porphyria</t>
+          <t>Amanita sp 61</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -4789,61 +4415,105 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Amanita cf. lavendula</t>
+          <t>Amanita sp longicuneus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>15</v>
+      </c>
+      <c r="E106" t="n">
+        <v>37</v>
+      </c>
+      <c r="F106" t="n">
+        <v>49.26666666666667</v>
+      </c>
+      <c r="G106" t="n">
+        <v>57</v>
+      </c>
+      <c r="H106" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J106" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>13</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>2</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Amanita cf. lavendula</t>
+          <t>Amanita sp NY06</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>11</v>
+      </c>
+      <c r="I107" t="n">
+        <v>11</v>
+      </c>
+      <c r="J107" t="n">
+        <v>11</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
@@ -4851,17 +4521,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Amanita porphyria</t>
+          <t>Amanita sp NY06</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -4882,30 +4552,52 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita sp NY06</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Validae</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>32</v>
+      </c>
+      <c r="F109" t="n">
+        <v>32</v>
+      </c>
+      <c r="G109" t="n">
+        <v>32</v>
+      </c>
+      <c r="H109" t="n">
+        <v>9</v>
+      </c>
+      <c r="I109" t="n">
+        <v>9</v>
+      </c>
+      <c r="J109" t="n">
+        <v>9</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -4913,17 +4605,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>30187_2</t>
+          <t>30226_2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita sp NY06</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4944,17 +4636,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>30187_3</t>
+          <t>30249_2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Amanita suballiacea</t>
+          <t>Amanita sp NY06</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Amanita</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4975,48 +4667,76 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>30193_2</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita sp.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
+          <t>Amidella</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12</v>
+      </c>
+      <c r="E112" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F112" t="n">
+        <v>44.66666666666666</v>
+      </c>
+      <c r="G112" t="n">
+        <v>51</v>
+      </c>
+      <c r="H112" t="n">
+        <v>9</v>
+      </c>
+      <c r="I112" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="J112" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K112" t="n">
+        <v>10</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4.590909090909091</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>30193_3</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita sp.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Amidella</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -5037,48 +4757,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>30194_2</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Amanita2</t>
+          <t>Amanita sp.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
+          <t>Validae</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F114" t="n">
+        <v>48.71428571428572</v>
+      </c>
+      <c r="G114" t="n">
+        <v>52</v>
+      </c>
+      <c r="H114" t="n">
+        <v>9</v>
+      </c>
+      <c r="I114" t="n">
+        <v>11.28571428571429</v>
+      </c>
+      <c r="J114" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P114" t="n">
+        <v>5.071428571428571</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>30199_2</t>
+          <t>30274_2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Amidella</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -5099,17 +4847,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>30199_3</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp. 'balmei'</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -5130,48 +4878,76 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>30199_4</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp. 61</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>48</v>
+      </c>
+      <c r="F117" t="n">
+        <v>65.375</v>
+      </c>
+      <c r="G117" t="n">
+        <v>77</v>
+      </c>
+      <c r="H117" t="n">
+        <v>13</v>
+      </c>
+      <c r="I117" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="J117" t="n">
+        <v>21</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P117" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>30204_2</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp. 61</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -5192,48 +4968,76 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>30204_3</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp. aurorae</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
+          <t>Vaginatae</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>7</v>
+      </c>
+      <c r="E119" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>38.64285714285715</v>
+      </c>
+      <c r="G119" t="n">
+        <v>42</v>
+      </c>
+      <c r="H119" t="n">
+        <v>10</v>
+      </c>
+      <c r="I119" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="J119" t="n">
+        <v>15</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P119" t="n">
+        <v>4.914285714285714</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>30204_4</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Amanita sub/am</t>
+          <t>Amanita sp. jakeslandingensis</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Phalloideae</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -5254,12 +5058,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>30208_2</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Amanita aff. citrina</t>
+          <t>Amanita sp. rubescens</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5285,17 +5089,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>30223_2</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita sp. subnigra</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Amanita</t>
+          <t>Vaginatae</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -5316,110 +5120,194 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>30223_3</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F123" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G123" t="n">
+        <v>44</v>
+      </c>
+      <c r="H123" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I123" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J123" t="n">
+        <v>12</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>8</v>
+      </c>
+      <c r="N123" t="n">
+        <v>2</v>
+      </c>
+      <c r="O123" t="n">
+        <v>6</v>
+      </c>
+      <c r="P123" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>30224_2</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Amanita multisquamosa</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>15</v>
+      </c>
+      <c r="E124" t="n">
+        <v>45</v>
+      </c>
+      <c r="F124" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>60</v>
+      </c>
+      <c r="H124" t="n">
+        <v>12</v>
+      </c>
+      <c r="I124" t="n">
+        <v>13.63333333333333</v>
+      </c>
+      <c r="J124" t="n">
+        <v>15</v>
+      </c>
+      <c r="K124" t="n">
+        <v>10</v>
+      </c>
+      <c r="L124" t="n">
+        <v>2</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P124" t="n">
+        <v>6.178571428571429</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>30226_2</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Amanita sp NY06</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12</v>
+      </c>
+      <c r="E125" t="n">
+        <v>44</v>
+      </c>
+      <c r="F125" t="n">
+        <v>53.54166666666666</v>
+      </c>
+      <c r="G125" t="n">
+        <v>67</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11</v>
+      </c>
+      <c r="I125" t="n">
+        <v>13.20833333333333</v>
+      </c>
+      <c r="J125" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>11</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P125" t="n">
+        <v>5.818181818181818</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>30230_2</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -5440,17 +5328,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>30230_3</t>
+          <t>30199_2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -5471,17 +5359,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>30230_4</t>
+          <t>30199_3</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -5502,17 +5390,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>30230_5</t>
+          <t>30199_4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -5533,17 +5421,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>30230_6</t>
+          <t>30204_2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -5564,17 +5452,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>30230_7</t>
+          <t>30204_3</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -5595,17 +5483,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>30230_8</t>
+          <t>30204_4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Amanita aff. rubescens</t>
+          <t>Amanita sub/am</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Validae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -5626,110 +5514,194 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>30239_2</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Amanita virginiana</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Caesareae</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>25</v>
+      </c>
+      <c r="E133" t="n">
+        <v>40</v>
+      </c>
+      <c r="F133" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="G133" t="n">
+        <v>52</v>
+      </c>
+      <c r="H133" t="n">
+        <v>10</v>
+      </c>
+      <c r="I133" t="n">
+        <v>12.688</v>
+      </c>
+      <c r="J133" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K133" t="n">
+        <v>13</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>10</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>3</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5.486363636363635</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>30249_2</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Amanita sp NY06</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Amanita</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>17</v>
+      </c>
+      <c r="E134" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>7</v>
+      </c>
+      <c r="I134" t="n">
+        <v>11.32352941176471</v>
+      </c>
+      <c r="J134" t="n">
+        <v>14</v>
+      </c>
+      <c r="K134" t="n">
+        <v>10</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>7.117647058823529</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>30250_2</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Amanita coryli</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
+          <t>Phalloideae</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>15</v>
+      </c>
+      <c r="E135" t="n">
+        <v>35</v>
+      </c>
+      <c r="F135" t="n">
+        <v>41.39285714285715</v>
+      </c>
+      <c r="G135" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H135" t="n">
+        <v>10</v>
+      </c>
+      <c r="I135" t="n">
+        <v>11.86666666666667</v>
+      </c>
+      <c r="J135" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>9</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>6</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>2</v>
+      </c>
+      <c r="P135" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>30257_2</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Amanita albiceps</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -5750,17 +5722,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>30274_2</t>
+          <t>30187_2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Amanita sp.</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Amidella</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -5781,17 +5753,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>30280_2</t>
+          <t>30187_3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita suballiacea</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Phalloideae</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -5812,79 +5784,135 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>30280_3</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita velatipes</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
+          <t>Amanita</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>7</v>
+      </c>
+      <c r="E139" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>43.28571428571428</v>
+      </c>
+      <c r="G139" t="n">
+        <v>49</v>
+      </c>
+      <c r="H139" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I139" t="n">
+        <v>11</v>
+      </c>
+      <c r="J139" t="n">
+        <v>12</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>6</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P139" t="n">
+        <v>5.642857142857143</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>30280_4</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita virginiana</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
+          <t>Caesareae</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F140" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H140" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I140" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J140" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" t="n">
+        <v>4</v>
+      </c>
+      <c r="P140" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>30280_5</t>
+          <t>30239_2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita virginiana</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Vaginatae</t>
+          <t>Caesareae</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -5905,12 +5933,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>30280_6</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5918,30 +5946,58 @@
           <t>Vaginatae</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>11</v>
+      </c>
+      <c r="E142" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>51</v>
+      </c>
+      <c r="G142" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="H142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I142" t="n">
+        <v>15.18181818181818</v>
+      </c>
+      <c r="J142" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>10</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>4</v>
+      </c>
+      <c r="P142" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>30280_7</t>
+          <t>30194_2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Amanita populiphila</t>
+          <t>Amanita2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5967,52 +6023,104 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>4</v>
+      </c>
+      <c r="E144" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F144" t="n">
+        <v>45</v>
+      </c>
+      <c r="G144" t="n">
+        <v>52</v>
+      </c>
+      <c r="H144" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J144" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>5</v>
+      </c>
+      <c r="P144" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>31+ species</t>
-        </is>
-      </c>
+          <t>30295</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F145" t="n">
+        <v>38.66666666666666</v>
+      </c>
+      <c r="G145" t="n">
+        <v>42</v>
+      </c>
+      <c r="H145" t="n">
+        <v>10</v>
+      </c>
+      <c r="I145" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>2</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>4</v>
+      </c>
+      <c r="P145" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6025,7 +6133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6122,12 +6230,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6136,150 +6244,146 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>30295</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>30295</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>no_numeric_in_fixed_range</t>
+          <t>ok_fixed_range</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30239</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30239</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -6287,77 +6391,71 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6366,27 +6464,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6408,70 +6506,66 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30213</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6480,27 +6574,27 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6509,114 +6603,108 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6625,27 +6713,27 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6654,56 +6742,54 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
-      </c>
-      <c r="G23" t="n">
-        <v>15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6712,27 +6798,27 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6741,27 +6827,27 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30222</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6773,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -6785,12 +6871,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30221</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6799,27 +6885,27 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6828,56 +6914,54 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30213</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6886,27 +6970,27 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6915,85 +6999,81 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30211(immature)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30211(immature)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30210(not found)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30210(not found)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ok_fixed_range</t>
+          <t>no_numeric_in_fixed_range</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
-      </c>
-      <c r="G33" t="n">
-        <v>15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7002,27 +7082,27 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7031,27 +7111,27 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7060,27 +7140,27 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7089,27 +7169,27 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7118,27 +7198,27 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30185</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7147,27 +7227,27 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7176,27 +7256,27 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7205,27 +7285,27 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7234,44 +7314,566 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>30199</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>30199</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>30198</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>30198</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>30197</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>30197</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>30196</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>30196</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>30195</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>30195</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>30194</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>30194</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>30193</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" t="n">
+        <v>14</v>
+      </c>
+      <c r="F49" t="n">
+        <v>15</v>
+      </c>
+      <c r="G49" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>30192</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>30192</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>30191</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>30191</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>14</v>
+      </c>
+      <c r="F51" t="n">
+        <v>15</v>
+      </c>
+      <c r="G51" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>30190</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>30190</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" t="n">
+        <v>15</v>
+      </c>
+      <c r="F52" t="n">
+        <v>15</v>
+      </c>
+      <c r="G52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>30189</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>30189</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>22</v>
+      </c>
+      <c r="E53" t="n">
+        <v>22</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22</v>
+      </c>
+      <c r="G53" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>30188</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>30188</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" t="n">
+        <v>13</v>
+      </c>
+      <c r="F54" t="n">
+        <v>15</v>
+      </c>
+      <c r="G54" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>30187</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>30187</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" t="n">
+        <v>15</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
+      <c r="G55" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>30186</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>30186</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" t="n">
+        <v>15</v>
+      </c>
+      <c r="F56" t="n">
+        <v>15</v>
+      </c>
+      <c r="G56" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>30185</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>30185</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17</v>
+      </c>
+      <c r="F58" t="n">
+        <v>17</v>
+      </c>
+      <c r="G58" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>30183</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25</v>
+      </c>
+      <c r="G59" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>30182</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>30182</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ok_fixed_range</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>22</v>
+      </c>
+      <c r="F60" t="n">
+        <v>25</v>
+      </c>
+      <c r="G60" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>30181</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>30181</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>ok_fixed_range</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D61" t="n">
         <v>24</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E61" t="n">
         <v>24</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F61" t="n">
         <v>24</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G61" t="n">
         <v>24</v>
       </c>
     </row>
